--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.66794657470145</v>
+        <v>2.708541318388985</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64718846194515</v>
+        <v>2.705168125066087</v>
       </c>
       <c r="E2" t="n">
-        <v>6.608660890520047</v>
+        <v>1.073907394709508</v>
       </c>
       <c r="F2" t="n">
-        <v>6.430147322566388</v>
+        <v>1.044898939917038</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88526835574154</v>
+        <v>4.856356107808001</v>
       </c>
       <c r="D3" t="n">
-        <v>29.50748310707792</v>
+        <v>4.794966004900163</v>
       </c>
       <c r="E3" t="n">
-        <v>6.608660890520047</v>
+        <v>1.073907394709508</v>
       </c>
       <c r="F3" t="n">
-        <v>6.430147322566388</v>
+        <v>1.044898939917038</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
